--- a/physician_forms/002_ophthalmology_referral_form--physician_forms.xlsx
+++ b/physician_forms/002_ophthalmology_referral_form--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'ophthalmologist'}</t>
+          <t>ophthalmologist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Ophthalmologist'}</t>
+          <t>Ophthalmologist</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'optometrist'}</t>
+          <t>optometrist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Optometrist'}</t>
+          <t>Optometrist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>referral_info_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'optometrist'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Optometrist'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'phone'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Phone'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'email'}</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Email'}</t>
+          <t>Fax</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'fax'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Fax'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'text':_'mail'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'text': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
